--- a/1_sinif/bahar/Ilk_Yardim_ve_Acil_Saglik_Hizmetleri_Soru_Bankasi.xlsx
+++ b/1_sinif/bahar/Ilk_Yardim_ve_Acil_Saglik_Hizmetleri_Soru_Bankasi.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,56 +25,16 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <sz val="10"/>
-    </font>
   </fonts>
-  <fills count="8">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="001B5E3A"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="001E3A8A"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00065F46"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="007A5800"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="009A3412"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00444444"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -82,48 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="00CCCCCC"/>
-      </left>
-      <right style="thin">
-        <color rgb="00CCCCCC"/>
-      </right>
-      <top style="thin">
-        <color rgb="00CCCCCC"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00CCCCCC"/>
-      </bottom>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -580,7 +504,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Cinsiyet birçok faktör vardır. Bunlardan bazıları; • Kanamanın hızı: Arter kanamaları gibi kanama hızının fazla olduğu durumlarda, daha fazla miktarda kan kaybedildiği için kanamanın ciddiye artar. • Kanama bölgesi: Kafa ve göğüs yaralanmalarındaki kanamalar gibi kanamanın haya organlarda olduğu durumlarda kanama ciddiye artar. • Kanama miktarı: Dolaşımdaki kanın %20’si akut olarak kaybedildiği zaman kalbin am hacmi %20‐40 oranında azalr. Bu nedenle kaybedilen kan miktarı arkça kanamanın ciddiye de artar. • Kişinin yaşı: Bebekler ve çocukların tolere edebileceği kan miktarı daha az olduğu için bu yaşlarda kanamanın ciddiye artar.</t>
+          <t>Cinsiyet</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -715,7 +639,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Uyuşturucu metabolik sorunlar;  Diyabet (şeker) hastalığı  Karaciğer yetmezlikleri  Üre artması  Ağır enfeksiyonlar  Nörolojik sorunlar  Sara (epilepsi)  Havale</t>
+          <t>Uyuşturucu</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1075,7 +999,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Röntgen teknisyeni doktor, hemşire, acil p teknisyeni (ATT), ambulans şoföründen oluşur</t>
+          <t>Röntgen teknisyeni</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1260,7 +1184,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Olay yerindeki toplam hasta sayısı saatleri,hekimin notu, hekimin kimliği, ikinci nakil ve birinci nakil bölümleri bulunmaktadır.</t>
+          <t>Olay yerindeki toplam hasta sayısı</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1350,7 +1274,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Zehirlenen kişinin bilinç düzeyi değerlendirilmelidir. Bilinci açık değilse ya da bulanık ise sıvı içecekler verilmemelidir. Yardım Uygulamaları  Müdahale eden kişinin kendisi ve hasta/yaralı için riskli bir ortam varsa hemen güvenli ortam sağlanmalıdır.  Zehirlenmelerin genel belirleri olan bulan, kusma, ishal ve bitkinlik durumu araşrılmalı ve hemen bir hastaneye ulaşrılmalıdır.  Zehirlenmeye neden olan madde zehirlenen kişi ve yakınlarından ayrınlı bir sorgulamayla tespit edilmeli, zehirli maddenin ne zaman, ne kadar miktarda ve hangi yolla alındığı belirlenmelidir. Zehirlenmelerde yapılması gereken ilk müdahaleler hava yolu açıklığının, solunum ve dolaşımın devamlılığının sağlanmasıdır. Zehirlenen kişi ve zehirli madde telefonun yanına gerilip 114 nolu zehir danışma merkezi aranmalıdır.  Kişinin yedikleri ve içkleri dikkatle sorgulanmalı ve not edilmelidir.  Zehir danışma merkezinden yönlendirici bilgi alınabilir.  Zehir danışma ha; 114,0800 314 79 00’dır. Bu telefona yapılacak olan danışmalar sonucunda özellikle hastaneye ulaşmada sıkın varsa zehirlenen kişinin durumunun ağırlaşması, bazen de gereksiz paniklerin ve işlemlerin yapılması önlenebilir.  Zehrin varsa ambalajı, şişesi veya kutusu zehirlenen kişi ile hastaneye götürülmelidir.  Zehirlenen kişinin bilinci açıksa, ağız yoluyla alınan zehrin yoğunluğunu azaltmak için su ve süt gibi sıvı içecekler verilir.  Asit ve alkalen dışındaki maddelerle zehirlenmelerde zehirlenen kişi kusturulmalıdır.  Kusturma için sıklıkla ipeka şurubu, daha az olarak da apomorfin en çok önerilen maddelerdir. Yoksa mekanik olarak farinksin parmakla uyarılması veya tuzlu ılık su içirilmesi ile kişilerin kusmaları sağlanmalıdır.  Zehirlenen kişi kusarsa kusmuğu bir poşete konarak nedenin bilinmediği durumlarda analiz için saklanmalıdır.  Zehirlenen kişinin bilinci kapalı ise koma ya da yan yaş pozisyonu verilmelidir. Baş‐çene manevrası yapılarak, dil kontrol edilerek soluk yolu açılmalı ve solunumu sağlanmalıdır.  Zehirlenen kişinin solunum ve nabzı kontrol edilmeli, eğer yoksa suni solunum ve kalp masajı uygulanmalıdır.  Zehirlenen kişinin bilinç düzeyi değerlendirilmelidir. Bilinci açık değilse ya da bulanık ise sıvı içecekler verilmemelidir.  Zehirlenen kişi yalnız bırakılmamalıdır.  Zehirli gazların solunmasına bağlı ortaya çıkan zehirlenmelerde kişiyi bulunduğu kapalı ortamdan uzaklaşrıp açık havaya çıkarmak ve varsa oksijen vermek gerekir. Bu yapılamıyorsa camlar açılarak içeriye temiz hava girmesi sağlanmalıdır.</t>
+          <t>Zehirlenen kişinin bilinç düzeyi değerlendirilmelidir. Bilinci</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1575,7 +1499,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Beşincil Korunma gönüllü kuruluşlar birlikte ve önceden hazırlanmış afet planına uygun olarak çalışmalıdır. Afetlerde görev alacak kişi ve kuruluşlar önceden belirlenmiş olmalıdır. Değişik kurum ve kuruluşların çalışmaları koordine edilmelidir. Sivil savunma teşkilatları, toplumun tüm kurum ve kuruluşları, iş birliği ve eşgüdüm içerisinde çalışmak zorundadır.</t>
+          <t>Beşincil Korunma</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1620,7 +1544,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>II ve III az tehlikeli iken geç zehirlenme yapan mantarlar çoğu kez ölümle sonuçlanır.</t>
+          <t>II ve III</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1665,7 +1589,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Linear kırık hastalığı gibi kemik ve kemik dokusunun fizyolojik yapısını bozan hastalıklar sonucu oluşan kırıkr.</t>
+          <t>Linear kırık</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1755,7 +1679,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Yaralı/hastanın yaşadığı paniğin sebebi araşrılmalı gerekirse sorular sorulmalıdır.</t>
+          <t>Yaralı/hastanın yaşadığı paniğin sebebi araşrılmalı gerekirse</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -1845,7 +1769,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Nodül birikmesidir. Yanıklar, donmalar vb. durumlarda oluşabilirkurtarıcı var ise iki parmak tekniği meme başlarından geçği varsayılan han hemen alna yerleşrilmelidir.</t>
+          <t>Nodül</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -1890,7 +1814,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Kollardan her biri % 9 CEVAP AN</t>
+          <t>Kollardan her biri % 9</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -1935,7 +1859,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Kırık sabitlenir. yaraya dokunulmaz.  Yaradan çıkan dokular içeri ilmez.  Yara yıkanmaz.  Temiz örtüyle yara kapalır  Kırık sabitlenir.</t>
+          <t>Kırık sabitlenir.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -1980,7 +1904,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Yaralının sağlık kuruluşuna sevki sağlanır. emniyene dikkat edilir. Yaralının yaşam bulguları değerlendirilir (CAB). Yara bölgesi, oluş şekli, süresi, yarada yabancı cismin varlığı, kanama durumu, şişlik, hassasiyet, şekil bozukluğu, fonksiyon kaybı yönünden değerlendirilir. Hemen 112 Acil Yardım Merkezinden bbi yardım istenir. Yaranın üzeri temiz bezle kapalır. Kanama varsa durdurulur. Yaranın içerisinde toz, toprak vb. yabancı maddeler varsa bol temiz su ile yıkanarak uzaklaşrılır. Pamuk, kağıt mendil, peçete vb. yara üzerinde, lif bırakıp kolayca dağılıp enfeksiyon riski oluşturmaları nedeniyle konulmaz. Gerekirse sargı bezi ile sarılır. Yaralı bölge kalp seviyesinin üzerinde tutulur. Yara bölgesinin hareke, ağrı ve kanamayı önlemek için engellenir. Yara içi kurcalanmaz. Ağız yolu ile yiyecek‐içecek verilmez. Isı kaybını önlemek için yaralının üzeri örtülür. Yaralı tetanos aşısı için yönlendirilir. Yaralının sağlık kuruluşuna sevki sağlanır.</t>
+          <t>Yaralının sağlık kuruluşuna sevki sağlanır.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2160,7 +2084,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Buharlaşma sıcaklığının 35°C alna düşmesidir. Vücuan radyasyon, konveksiyon, kondüksiyon, buharlaşma yolları ile ısı kaybedilir.</t>
+          <t>Buharlaşma</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2430,7 +2354,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Boyna asarak sürükleme bileklerinden tutarak sürükleme Koltuk alndan tutarak sürükleme Baaniye ile sürükleme, Boyna asarak sürükleme</t>
+          <t>Boyna asarak sürükleme</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2700,7 +2624,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Alkol, anbiyok içeren merhem, pudra vb. maddeler yara üzerine uygulanır. anbiyok içeren merhem, pudra vb. maddeler yaranın tahrişine neden olacağından yara üzerine uygulanmaz, Yaranın üzeri temiz bezle kapalır, Kanama varsa durdurulur, Yaralı bölge kalp seviyesinin üzerinde tutulur, Yara bölgesinin hareke, ağrı ve kanamayı önlemek için engellenir.</t>
+          <t>Alkol, anbiyok içeren merhem, pudra vb. maddeler yara</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3555,7 +3479,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Bak‐dinle‐hisset yöntemi ile 5‐10 saniye dinlenir. yolu uygun bir şekilde açıldıktan sonra, hava yolu açık tutularak çocuk veya bebeğin solunumu 5–10 sn. içinde kontrol edilir. Eğer çocuk veya bebekte solunumun olup olmadığına karar verilemedi ise solunum yokmuş gibi hareket edilir</t>
+          <t>Bak‐dinle‐hisset yöntemi ile 5‐10 saniye dinlenir.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -3738,7 +3662,6 @@
           <t>Tansiyon alenin manşonu turnike olarak kullanılabilir.</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr">
         <is>
           <t>🚫 İptal edilmiş soru</t>
@@ -4321,7 +4244,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Bireyin nöbet geçireceği hissedildiği zaman ilk alınması gereken önlem bireyin zarar görmesini engellemekr.</t>
+          <t>Bireyin nöbet geçireceği hissedildiği zaman ilk alınması gereken</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -4366,7 +4289,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Kasılmalar durduktan sonra, bireye koma pozisyonu verilmeli rahatlalarak bireyin uyuması sağlanmalıdır. yardım  Bireyin nöbet geçireceği hissedildiği zaman ilk alınması gereken önlem bireyin zarar görmesini engellemekr.  Öncelikle, olayla ilgili güvenlik önlemleri alınmalıdır.  Hasta güvenli bir yere yarılmalıdır.  Başın alna yumuşak malzeme konularak yaralanma önlenmeye çalışılmalıdır.  Bireyin boynunu sıkan giysiler gevşelmelidir.  Nöbet başladıktan sonra çene kilitlenmiş ise açılmaya çalışılmamalıdır.  Bireyin nöbet geçireceği hissedilirse dişlerinin arasına rulo yapılmış bir mendil, solunum yolunu kamayacak şekilde yerleşrilerek dil ve dişler korunmaya çalışılmalıdır.  Hasta bağlanmamalı, sıkıca tutulmamalı, kriz sürecinin tamamlanması beklenmelidir.  Soğuk su dökme, soğan, kolonya koklatma ya da tokat atma gibi uyaranlardandan kaçınılmalıdır.  Kasılmalar durduktan sonra, bireye koma pozisyonu verilmeli rahatlalarak bireyin uyuması sağlanmalıdır.  Tıbbi yardım 112’den istenmelidir.</t>
+          <t>Kasılmalar durduktan sonra, bireye koma pozisyonu</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -4411,7 +4334,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Hastaya cevaplaması için soru sorulur. dokunulmalı “iyi misin?” diye yüksek sesle sorulmalı, adı biliniyorsa adıyla seslenilmelidir. Bebeğin ise ayak tabanına hafifçe vurularak bilinci kontrol edilmelidir. Çocuk veya bebek hareket eder, inler ya da cevap verirse hızla herhangi bir yaralanma ya da bbi yardım ihyacı olup olmadığına bakılmalı acil yardım sistemi akve edilmelidir.</t>
+          <t>Hastaya cevaplaması için soru sorulur.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -4504,7 +4427,6 @@
           <t>I-II-IV-III-V CEVAP AN</t>
         </is>
       </c>
-      <c r="I89" t="inlineStr"/>
       <c r="J89" t="inlineStr">
         <is>
           <t>🚫 İptal edilmiş soru</t>
@@ -4547,7 +4469,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>I ve III deri soluk ve nemlidir. Terleme nedeniyle vücut sıcaklığı düşük, normal veya yüksek olabilir. Pupiller küçüktür. Cilt kuru ve sıcakr. ifadesi sıcak çarpmasının belirlerindendir.</t>
+          <t>I ve III</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -4862,7 +4784,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>I ve II denilen afetleri de germektedir. Örneğin; deprem, tsunami, heyelan, salgın hastalıklara neden olabilir.</t>
+          <t>I ve II</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -5042,7 +4964,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Göğüs kemiğinin alt ve üst ucu tespit edilerek alt yarısına bir elin topuğu ile uygulanır.</t>
+          <t>Göğüs kemiğinin alt ve üst ucu tespit edilerek</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -5132,7 +5054,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Kuru kimyasal maddelere maruz kalındığında bu maddeler kuru olarak yavaşça rçalanmalıdır.</t>
+          <t>Kuru kimyasal maddelere maruz kalındığında bu maddeler</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -5267,7 +5189,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Hasta/yaralıya müdahalede yardımcı olacak kişileri organize etmeli ve yönlendirmelidir. gerekenler: Öncelik ve ivedilikle olay yeri incelenip, güvenliği sağlanır. • Hasta/yaralının korku ve endişeleri giderilir. • Hasta/yaralıya müdahalede yardımcı olacak kişileri organize edilir ve yönlendirilir. • Solunum ve kalp durması, kanama, şok ve ağır yaralanma gibi yaşamsal tehlike oluşturan durumlara öncelikle müdahale edilir. • Hasta ya da yaralıların en uygun yöntemlerle en yakın sağlık kuruluşuna sevki sağlanır.</t>
+          <t>Hasta/yaralıya müdahalede yardımcı olacak kişileri</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -5405,7 +5327,6 @@
           <t>%27</t>
         </is>
       </c>
-      <c r="I109" t="inlineStr"/>
       <c r="J109" t="inlineStr">
         <is>
           <t>🚫 İptal edilmiş soru</t>
@@ -5448,7 +5369,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>%45 hesaplanmasında özel tablolar kullanılmaktadır, prakte en fazla kullanılan Pulaski ve Wallece’nin ortaya koyduğu DOKUZLAR KURALI’dır Tedavi için yanık genişliğinin tespinde dokuzlar kuralına göre yanık yüzdesi aşağıdaki şekilde hesaplanabilir.  Baş % 9  Kollardan her biri % 9  Bacaklardan her biri % 18  Gövdenin ön tara % 18  Gövdenin arka tara % 18  Üreme organları % 1</t>
+          <t>%45</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -5851,7 +5772,6 @@
           <t>Yılanın soktuğu yerin 5‐10 cm yukarısından 1‐</t>
         </is>
       </c>
-      <c r="H119" t="inlineStr"/>
       <c r="I119" t="inlineStr">
         <is>
           <t>A</t>
@@ -6029,7 +5949,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Kuintuser triyaj yaralıların eldeki imkânlar doğrultusunda olay yerinden nakillerinin önceliklerini belirleyerek hastaneye nakillerini hedefler.</t>
+          <t>Kuintuser triyaj</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">

--- a/1_sinif/bahar/Ilk_Yardim_ve_Acil_Saglik_Hizmetleri_Soru_Bankasi.xlsx
+++ b/1_sinif/bahar/Ilk_Yardim_ve_Acil_Saglik_Hizmetleri_Soru_Bankasi.xlsx
@@ -512,6 +512,7 @@
           <t>E</t>
         </is>
       </c>
+      <c r="J2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -557,6 +558,7 @@
           <t>A</t>
         </is>
       </c>
+      <c r="J3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -594,7 +596,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Hastaya bol miktarda ağızdan sıvı verilir. NAHTARI</t>
+          <t>Hastaya bol miktarda ağızdan sıvı verilir.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -602,6 +604,7 @@
           <t>E</t>
         </is>
       </c>
+      <c r="J4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -647,6 +650,7 @@
           <t>E</t>
         </is>
       </c>
+      <c r="J5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -692,6 +696,7 @@
           <t>E</t>
         </is>
       </c>
+      <c r="J6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -737,6 +742,7 @@
           <t>C</t>
         </is>
       </c>
+      <c r="J7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -782,6 +788,7 @@
           <t>D</t>
         </is>
       </c>
+      <c r="J8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -827,6 +834,7 @@
           <t>D</t>
         </is>
       </c>
+      <c r="J9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -864,7 +872,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Kişiye hava akımı sağlanmalı CEVAP AN</t>
+          <t>Kişiye hava akımı sağlanmalı</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -872,6 +880,7 @@
           <t>E</t>
         </is>
       </c>
+      <c r="J10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -917,6 +926,7 @@
           <t>D</t>
         </is>
       </c>
+      <c r="J11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -962,6 +972,7 @@
           <t>E</t>
         </is>
       </c>
+      <c r="J12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1007,6 +1018,7 @@
           <t>E</t>
         </is>
       </c>
+      <c r="J13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1052,6 +1064,7 @@
           <t>A</t>
         </is>
       </c>
+      <c r="J14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1147,6 +1160,7 @@
           <t>E</t>
         </is>
       </c>
+      <c r="J16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1192,6 +1206,7 @@
           <t>E</t>
         </is>
       </c>
+      <c r="J17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1237,6 +1252,7 @@
           <t>B</t>
         </is>
       </c>
+      <c r="J18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1282,6 +1298,7 @@
           <t>D</t>
         </is>
       </c>
+      <c r="J19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1327,6 +1344,7 @@
           <t>A</t>
         </is>
       </c>
+      <c r="J20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1364,7 +1382,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Üç atel ile tespit NAHTARI</t>
+          <t>Üç atel ile tespit</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1372,6 +1390,7 @@
           <t>E</t>
         </is>
       </c>
+      <c r="J21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1417,6 +1436,7 @@
           <t>E</t>
         </is>
       </c>
+      <c r="J22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1462,6 +1482,7 @@
           <t>B</t>
         </is>
       </c>
+      <c r="J23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1507,6 +1528,7 @@
           <t>C</t>
         </is>
       </c>
+      <c r="J24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1552,6 +1574,7 @@
           <t>A</t>
         </is>
       </c>
+      <c r="J25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1597,6 +1620,7 @@
           <t>B</t>
         </is>
       </c>
+      <c r="J26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1642,6 +1666,7 @@
           <t>E</t>
         </is>
       </c>
+      <c r="J27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1687,6 +1712,7 @@
           <t>D</t>
         </is>
       </c>
+      <c r="J28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1732,6 +1758,7 @@
           <t>C</t>
         </is>
       </c>
+      <c r="J29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1777,6 +1804,7 @@
           <t>A</t>
         </is>
       </c>
+      <c r="J30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1822,6 +1850,7 @@
           <t>A</t>
         </is>
       </c>
+      <c r="J31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1867,6 +1896,7 @@
           <t>C</t>
         </is>
       </c>
+      <c r="J32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1912,6 +1942,7 @@
           <t>B</t>
         </is>
       </c>
+      <c r="J33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1957,6 +1988,7 @@
           <t>A</t>
         </is>
       </c>
+      <c r="J34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -2002,6 +2034,7 @@
           <t>B</t>
         </is>
       </c>
+      <c r="J35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -2047,6 +2080,7 @@
           <t>A</t>
         </is>
       </c>
+      <c r="J36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -2092,6 +2126,7 @@
           <t>D</t>
         </is>
       </c>
+      <c r="J37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -2137,6 +2172,7 @@
           <t>C</t>
         </is>
       </c>
+      <c r="J38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -2182,6 +2218,7 @@
           <t>D</t>
         </is>
       </c>
+      <c r="J39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -2227,6 +2264,7 @@
           <t>D</t>
         </is>
       </c>
+      <c r="J40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -2272,6 +2310,7 @@
           <t>B</t>
         </is>
       </c>
+      <c r="J41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -2317,6 +2356,7 @@
           <t>B</t>
         </is>
       </c>
+      <c r="J42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -2362,6 +2402,7 @@
           <t>C</t>
         </is>
       </c>
+      <c r="J43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -2399,7 +2440,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Risk yönemi CEVAP AN</t>
+          <t>Risk yönemi</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -2407,6 +2448,7 @@
           <t>C</t>
         </is>
       </c>
+      <c r="J44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -2452,6 +2494,7 @@
           <t>E</t>
         </is>
       </c>
+      <c r="J45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -2497,6 +2540,7 @@
           <t>D</t>
         </is>
       </c>
+      <c r="J46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -2542,6 +2586,7 @@
           <t>A</t>
         </is>
       </c>
+      <c r="J47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -2587,6 +2632,7 @@
           <t>B</t>
         </is>
       </c>
+      <c r="J48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -2632,6 +2678,7 @@
           <t>E</t>
         </is>
       </c>
+      <c r="J49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -2677,6 +2724,7 @@
           <t>B</t>
         </is>
       </c>
+      <c r="J50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -2722,6 +2770,7 @@
           <t>B</t>
         </is>
       </c>
+      <c r="J51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -2767,6 +2816,7 @@
           <t>D</t>
         </is>
       </c>
+      <c r="J52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -2812,6 +2862,7 @@
           <t>D</t>
         </is>
       </c>
+      <c r="J53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -2857,6 +2908,7 @@
           <t>C</t>
         </is>
       </c>
+      <c r="J54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -2894,7 +2946,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Aynı anda birden fazla iş yapması NAHTARI</t>
+          <t>Aynı anda birden fazla iş yapması</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -2902,6 +2954,7 @@
           <t>A</t>
         </is>
       </c>
+      <c r="J55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -2947,6 +3000,7 @@
           <t>B</t>
         </is>
       </c>
+      <c r="J56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -2984,7 +3038,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Dolaşım NAHTARI</t>
+          <t>Dolaşım</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -2992,6 +3046,7 @@
           <t>C</t>
         </is>
       </c>
+      <c r="J57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -3037,6 +3092,7 @@
           <t>A</t>
         </is>
       </c>
+      <c r="J58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -3082,6 +3138,7 @@
           <t>B</t>
         </is>
       </c>
+      <c r="J59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -3127,6 +3184,7 @@
           <t>B</t>
         </is>
       </c>
+      <c r="J60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -3172,6 +3230,7 @@
           <t>D</t>
         </is>
       </c>
+      <c r="J61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -3217,6 +3276,7 @@
           <t>B</t>
         </is>
       </c>
+      <c r="J62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -3262,6 +3322,7 @@
           <t>B</t>
         </is>
       </c>
+      <c r="J63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -3307,6 +3368,7 @@
           <t>A</t>
         </is>
       </c>
+      <c r="J64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -3344,7 +3406,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Hastanın söylenenleri anlayıp anlamadığı kontrol edilmelidir. kısmının büyük bir hasarıdır. Hasta/yaralı acil servise bilinci kapalı şekilde gerilebileceği gibi hastanın normal durumunda küçük değişiklikler sonrası bile konfüze olabilir. Konfüze hasta/yaralı ile ileşimde;  Basit cümleler kullanılmalıdır.  Basit örneklerle açıklama yapılmalıdır.  Hasta/yaralının yanıt vermesi için yeterli zaman tanınmalıdır.  Hastanın söylenenleri anlayıp anlamadığı kontrol edilmelidir.</t>
+          <t>Hastanın söylenenleri anlayıp anlamadığı kontrol edilmelidir.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -3352,6 +3414,7 @@
           <t>B</t>
         </is>
       </c>
+      <c r="J65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -3397,6 +3460,7 @@
           <t>A</t>
         </is>
       </c>
+      <c r="J66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -3442,6 +3506,7 @@
           <t>C</t>
         </is>
       </c>
+      <c r="J67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -3487,6 +3552,7 @@
           <t>E</t>
         </is>
       </c>
+      <c r="J68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -3532,6 +3598,7 @@
           <t>E</t>
         </is>
       </c>
+      <c r="J69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -3577,6 +3644,7 @@
           <t>E</t>
         </is>
       </c>
+      <c r="J70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -3622,6 +3690,7 @@
           <t>C</t>
         </is>
       </c>
+      <c r="J71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -3662,6 +3731,7 @@
           <t>Tansiyon alenin manşonu turnike olarak kullanılabilir.</t>
         </is>
       </c>
+      <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr">
         <is>
           <t>🚫 İptal edilmiş soru</t>
@@ -3712,6 +3782,7 @@
           <t>A</t>
         </is>
       </c>
+      <c r="J73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -3757,6 +3828,7 @@
           <t>D</t>
         </is>
       </c>
+      <c r="J74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -3802,6 +3874,7 @@
           <t>B</t>
         </is>
       </c>
+      <c r="J75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -3847,6 +3920,7 @@
           <t>E</t>
         </is>
       </c>
+      <c r="J76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -3892,6 +3966,7 @@
           <t>C</t>
         </is>
       </c>
+      <c r="J77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -3937,6 +4012,7 @@
           <t>A</t>
         </is>
       </c>
+      <c r="J78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -3982,6 +4058,7 @@
           <t>E</t>
         </is>
       </c>
+      <c r="J79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -4027,6 +4104,7 @@
           <t>D</t>
         </is>
       </c>
+      <c r="J80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -4072,6 +4150,7 @@
           <t>D</t>
         </is>
       </c>
+      <c r="J81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -4109,7 +4188,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Beynin faaliyetlerindeki aksama sonucu çok derin bilinç kaybıdır. CEVAP AN</t>
+          <t>Beynin faaliyetlerindeki aksama sonucu çok derin bilinç kaybıdır.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -4117,6 +4196,7 @@
           <t>A</t>
         </is>
       </c>
+      <c r="J82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -4162,6 +4242,7 @@
           <t>D</t>
         </is>
       </c>
+      <c r="J83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -4207,6 +4288,7 @@
           <t>E</t>
         </is>
       </c>
+      <c r="J84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -4252,6 +4334,7 @@
           <t>C</t>
         </is>
       </c>
+      <c r="J85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -4297,6 +4380,7 @@
           <t>D</t>
         </is>
       </c>
+      <c r="J86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -4342,6 +4426,7 @@
           <t>E</t>
         </is>
       </c>
+      <c r="J87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -4387,6 +4472,7 @@
           <t>E</t>
         </is>
       </c>
+      <c r="J88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -4424,9 +4510,10 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>I-II-IV-III-V CEVAP AN</t>
-        </is>
-      </c>
+          <t>I-II-IV-III-V</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
       <c r="J89" t="inlineStr">
         <is>
           <t>🚫 İptal edilmiş soru</t>
@@ -4477,6 +4564,7 @@
           <t>C</t>
         </is>
       </c>
+      <c r="J90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -4522,6 +4610,7 @@
           <t>E</t>
         </is>
       </c>
+      <c r="J91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -4567,6 +4656,7 @@
           <t>B</t>
         </is>
       </c>
+      <c r="J92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -4612,6 +4702,7 @@
           <t>C</t>
         </is>
       </c>
+      <c r="J93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -4657,6 +4748,7 @@
           <t>C</t>
         </is>
       </c>
+      <c r="J94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -4694,7 +4786,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>I, II, III ve IV NAHTARI</t>
+          <t>I, II, III ve IV</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -4702,6 +4794,7 @@
           <t>D</t>
         </is>
       </c>
+      <c r="J95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -4747,6 +4840,7 @@
           <t>C</t>
         </is>
       </c>
+      <c r="J96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -4792,6 +4886,7 @@
           <t>D</t>
         </is>
       </c>
+      <c r="J97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -4837,6 +4932,7 @@
           <t>C</t>
         </is>
       </c>
+      <c r="J98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -4882,6 +4978,7 @@
           <t>E</t>
         </is>
       </c>
+      <c r="J99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -4919,7 +5016,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Bilinç açıksa yarı oturur pozisyon verilmelidir. NAHTARI</t>
+          <t>Bilinç açıksa yarı oturur pozisyon verilmelidir.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -4927,6 +5024,7 @@
           <t>A</t>
         </is>
       </c>
+      <c r="J100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -4972,6 +5070,7 @@
           <t>E</t>
         </is>
       </c>
+      <c r="J101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -5009,7 +5108,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Ven kanamaları CEVAP AN</t>
+          <t>Ven kanamaları</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -5017,6 +5116,7 @@
           <t>A</t>
         </is>
       </c>
+      <c r="J102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -5062,6 +5162,7 @@
           <t>C</t>
         </is>
       </c>
+      <c r="J103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -5107,6 +5208,7 @@
           <t>C</t>
         </is>
       </c>
+      <c r="J104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -5152,6 +5254,7 @@
           <t>C</t>
         </is>
       </c>
+      <c r="J105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -5197,6 +5300,7 @@
           <t>D</t>
         </is>
       </c>
+      <c r="J106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -5242,6 +5346,7 @@
           <t>D</t>
         </is>
       </c>
+      <c r="J107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -5287,6 +5392,7 @@
           <t>E</t>
         </is>
       </c>
+      <c r="J108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -5327,6 +5433,7 @@
           <t>%27</t>
         </is>
       </c>
+      <c r="I109" t="inlineStr"/>
       <c r="J109" t="inlineStr">
         <is>
           <t>🚫 İptal edilmiş soru</t>
@@ -5377,6 +5484,7 @@
           <t>D</t>
         </is>
       </c>
+      <c r="J110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -5422,6 +5530,7 @@
           <t>C</t>
         </is>
       </c>
+      <c r="J111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -5459,7 +5568,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Acil Sağlık Hizmetleri Genel Müdürlüğü NAHTARI</t>
+          <t>Acil Sağlık Hizmetleri Genel Müdürlüğü</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -5467,6 +5576,7 @@
           <t>E</t>
         </is>
       </c>
+      <c r="J112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -5512,6 +5622,7 @@
           <t>A</t>
         </is>
       </c>
+      <c r="J113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -5557,6 +5668,7 @@
           <t>B</t>
         </is>
       </c>
+      <c r="J114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -5602,6 +5714,7 @@
           <t>B</t>
         </is>
       </c>
+      <c r="J115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -5647,6 +5760,7 @@
           <t>A</t>
         </is>
       </c>
+      <c r="J116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -5692,6 +5806,7 @@
           <t>B</t>
         </is>
       </c>
+      <c r="J117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -5737,6 +5852,7 @@
           <t>C</t>
         </is>
       </c>
+      <c r="J118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -5772,11 +5888,13 @@
           <t>Yılanın soktuğu yerin 5‐10 cm yukarısından 1‐</t>
         </is>
       </c>
+      <c r="H119" t="inlineStr"/>
       <c r="I119" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
+      <c r="J119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -5822,6 +5940,7 @@
           <t>C</t>
         </is>
       </c>
+      <c r="J120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -5867,6 +5986,7 @@
           <t>A</t>
         </is>
       </c>
+      <c r="J121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -5912,6 +6032,7 @@
           <t>B</t>
         </is>
       </c>
+      <c r="J122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -5957,6 +6078,7 @@
           <t>C</t>
         </is>
       </c>
+      <c r="J123" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
